--- a/02_DIA_inicio_2026_analisis_assets/rbd_9706_escuela-bas-oscar-encalada-yovanovich_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9706_escuela-bas-oscar-encalada-yovanovich_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D375C1BA-924A-4493-A982-0958BF7AD863}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17FD24D1-1D9D-4A51-A498-48BB1475816B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{199E294A-F608-4C07-A424-BF591849464E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AF35163-C371-498A-9FF0-61E7F6BC93A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E234D7-52EE-48ED-B14F-0C39A98B4919}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{256C7A3D-6DBB-46C8-9503-ABE8D75975F2}"/>
 </file>